--- a/output/AUDIT-STAT-REPORT-p0-2026-08-02.xlsx
+++ b/output/AUDIT-STAT-REPORT-p0-2026-08-02.xlsx
@@ -774,11 +774,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>p0 compiled into a real, runnable Check (incl. 241 scenario-gated stubs unlocked 2026-08-01)</t>
+          <t>p0 compiled into a real, runnable Check (incl. 401 scenario-gated stubs, resolve6+resolve7)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>506</v>
+        <v>666</v>
       </c>
     </row>
     <row r="33">
@@ -788,13 +788,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>599</v>
+        <v>439</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5. p0 verdict distribution, THIS loan (12607601215), refreshed after the 2026-08-01 resolve6 pass</t>
+          <t>5. p0 verdict distribution, THIS loan (12607601215), refreshed after the 2026-08-01 resolve6+resolve7 passes</t>
         </is>
       </c>
     </row>
@@ -827,11 +827,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>284</v>
+        <v>443</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>599</v>
+        <v>439</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -957,11 +957,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE parity after the resolve6 pass (both engines)</t>
+          <t>NOT_APPLICABLE parity after resolve6+resolve7 (both engines)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>284</v>
+        <v>443</v>
       </c>
     </row>
     <row r="48">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>259</v>
+        <v>418</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -1832,40 +1832,40 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>The rule text cites a number/threshold, but the wording is ambiguous about direction ("&gt;", "&lt;", "not met") -- the compiler correctly refuses to guess rather than invent a threshold not clearly stated in the source.</t>
+          <t>The document itself is not curated to a real Touchless document type AND the check only applies under a scenario/fact this project cannot yet resolve. Needs both a document-vendor mapping and new fact-derivation logic.</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Custodial Acct</t>
+          <t>O-CFPB-14500</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Were the funds from an acceptable source when a custodial account was utilized?</t>
+          <t>(Best Practice) Were all Limited English Proficiency (LEP) requirements met?</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Custodial Acct</t>
+          <t>O-CFPB-54136</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>A custodial account that is an irrevocable trust like Uniform Transfer to Minors Act (UTMA) and Uniform Gifts to Minors Act (UGMA) are ineligible source of funds, including as source of funds for large deposits.</t>
+          <t>(Best Practice) The borrower was not provided with a clear and timely Limited English Proficiency (LEP) disclosure in non-English languages at the time of application that describes the extent and limits of any language services provided throughout the product lifecycle.</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
+          <t>Only applies when the borrower is a Limited English Proficiency individual, a fact not knowable from the document inventory alone.</t>
         </is>
       </c>
     </row>
@@ -1877,40 +1877,40 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
+          <t>NOT_COMPILED_PRESENCE_GATE_NEEDS_CONDITIONAL_LOGIC</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>The document itself is not curated to a real Touchless document type AND the check only applies under a scenario/fact this project cannot yet resolve. Needs both a document-vendor mapping and new fact-derivation logic.</t>
+          <t>One document's presence or absence should gate whether a DIFFERENT requirement applies -- needs real conditional-check logic that doesn't exist yet.</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>O-CFPB-14500</t>
+          <t>Final URLA</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>(Best Practice) Were all Limited English Proficiency (LEP) requirements met?</t>
+          <t>Have all sections of the Final 1003 been completed and accurate?</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>O-CFPB-54136</t>
+          <t>URLA-Final-2</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>(Best Practice) The borrower was not provided with a clear and timely Limited English Proficiency (LEP) disclosure in non-English languages at the time of application that describes the extent and limits of any language services provided throughout the product lifecycle.</t>
+          <t>The final 1003 application is inaccurate or incomplete</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Only applies when the borrower is a Limited English Proficiency individual, a fact not knowable from the document inventory alone.</t>
+          <t>The Final URLA/1003 must not only exist but have all sections completed and accurate; a completeness/accuracy content check goes beyond mere presence, and no exact closed-list form name is used in the prose.</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>O-FNM-15334</t>
+          <t>O-FED-14507</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Were all verification of deposit assets requirements met?</t>
+          <t>Were all federal Higher-Priced Mortgage Loan (HPML) requirements met?</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>O-FNM-54872</t>
+          <t>O-TILA-54206</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>The subject limited or cash-out refinance transaction did not contain the most recent 1 month period of account activity (30 days) of bank statements or investment portfolio statements.</t>
+          <t>In a higher-priced mortgage loan, a copy of each written appraisal was not provided to the consumer no later than three business days prior to consummation of the loan.</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -1967,15 +1967,15 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_PRESENCE_GATE_NEEDS_CONDITIONAL_LOGIC</t>
+          <t>NOT_COMPILED_CROSS_DOC_NO_CURATED_COMPARISON</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>One document's presence or absence should gate whether a DIFFERENT requirement applies -- needs real conditional-check logic that doesn't exist yet.</t>
+          <t>This rule needs comparing two different documents against each other -- no curated multi-document comparison logic exists yet.</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>URLA-Final-2</t>
+          <t>URLA-Final-9</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>The final 1003 application is inaccurate or incomplete</t>
+          <t>The employment dates listed on the 1003 do not match other employment documentation in the file</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>The Final URLA/1003 must not only exist but have all sections completed and accurate; a completeness/accuracy content check goes beyond mere presence, and no exact closed-list form name is used in the prose.</t>
+          <t>Rule requires comparing two documents to each other; no curated comparison logic exists yet (compile-time gap)</t>
         </is>
       </c>
     </row>
@@ -2012,40 +2012,40 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_CROSS_DOC_NO_CURATED_COMPARISON</t>
+          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>This rule needs comparing two different documents against each other -- no curated multi-document comparison logic exists yet.</t>
+          <t>The rule text cites a number/threshold, but the wording is ambiguous about direction ("&gt;", "&lt;", "not met") -- the compiler correctly refuses to guess rather than invent a threshold not clearly stated in the source.</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Final URLA</t>
+          <t>Custodial Acct</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Have all sections of the Final 1003 been completed and accurate?</t>
+          <t>Were the funds from an acceptable source when a custodial account was utilized?</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>URLA-Final-9</t>
+          <t>Custodial Acct</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>The employment dates listed on the 1003 do not match other employment documentation in the file</t>
+          <t>A custodial account that is an irrevocable trust like Uniform Transfer to Minors Act (UTMA) and Uniform Gifts to Minors Act (UGMA) are ineligible source of funds, including as source of funds for large deposits.</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Rule requires comparing two documents to each other; no curated comparison logic exists yet (compile-time gap)</t>
+          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
         </is>
       </c>
     </row>
@@ -4160,20 +4160,24 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (lender incentive paying off the loan being refinanced); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4454,20 +4458,24 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Only applies when the borrower is a non-US citizen with recent deposits, a borrower attribute not determinable from document-type inventory alone.</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+          <t>Trigger requires a non-US-citizen borrower (with recent deposits into a US depository); the sole borrower's URLA declaration is extracted: declaration.citizenshipResidencyType='USCitizen', and borrowerPairs[0].borrowers contains exactly one borrower -- the trigger is provably false for every applicant. (Replaces existing UNKNOWN row, whose reason 'non-US-citizen status not established' is contradicted by this extracted field.)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4570,20 +4578,24 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (limited or cash-out refinance transaction); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4996,20 +5008,24 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Only applies when a gift of equity was used, which is not inferable from document-type inventory, though the required gift letter is named and matches the closed vocabulary.</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>Trigger requires a gift of equity in the transaction; the only gift evidenced is positively typed assetDetail.assets[0].assetType='GIFT_OF_CASH' (fundSourceType='RELATIVE', 10000.0), a distinct enum from a gift of equity. Corroborating independent signals (assetDetail is not closed-world): declaration.specialBorrowerSellerRelationIndicator='N' and exactly one Gift Letter documents[11] matching the cash gift. (Replaces existing UNKNOWN row, whose reason 'nothing indicates cash vs equity' is contradicted by the extracted assetType.)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5054,20 +5070,24 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
+          <t>Trigger requires a gift of equity used as financial reserves; the only gift evidenced is positively typed assetDetail.assets[0].assetType='GIFT_OF_CASH' (fundSourceType='RELATIVE', 10000.0) -- a cash gift, not a gift of equity. Corroborating independent signals (assetDetail is not closed-world): declaration.specialBorrowerSellerRelationIndicator='N' (no borrower-seller relationship, which a gift of equity presupposes) and exactly one Gift Letter documents[11] matching the cash gift.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5410,20 +5430,24 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+          <t>Trigger requires donated grant funds in the transaction; the only gift-type asset is positively typed assetType='GIFT_OF_CASH' with fundSourceType='RELATIVE' (a grant's source would be an agency/employer/nonprofit enum), and the closed-world documents[] contains no grant-award/grant-program documentType (funds docs: VOA x2, Bank Statement x2, Gift Letter).</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6130,20 +6154,24 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
+          <t>Trigger requires a rent-back credit under a documented lease/option-to-purchase arrangement; the closed-world documents[] contains no lease, rental agreement, or option-to-purchase documentType, and the sale is a standard Purchase Agreement documents[13].</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6374,20 +6402,24 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
+          <t>Trigger requires sweat equity used as a source of funds; sweat equity must be documented in file (appraiser valuation of labor/materials, sweat-equity agreement) and the closed-world documents[] contains no such documentType; the evidenced funds are VOA x2, Bank Statement x2, and a cash gift (assetDetail.assets[0].assetType='GIFT_OF_CASH').</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6494,20 +6526,24 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
+          <t>Trigger requires a bridge/swing loan in the transaction; the borrower's only owned property is positively marked ownedPropertyDispositionStatusType='RetainForRental' (no pending sale to bridge), and the closed-world documents[] contains no bridge-loan documentType; down-payment funds are evidenced by VOA x2 / Bank Statement x2 / Gift Letter.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8050,20 +8086,24 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust. The co-op conjunct is independently false: attachmentType='Detached', cooperativeIndicator=null, PUD Rider in file.</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8232,20 +8272,24 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8704,20 +8748,24 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>REAL_DATA_MATCH</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr"/>
+          <t>FIELD_VALUE 360.0% &lt;= 360.0%</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>FIELD_VALUE 360.0% &lt;= 360.0%</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11292,20 +11340,24 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr"/>
+          <t>Trigger requires the loan to have been modified due to a principal curtailment with the balance recast; the closed-world 62-entry documents[] contains no loan modification/recast agreement documentType -- a modification must be documented in the closed file.</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12286,20 +12338,24 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr"/>
+          <t>Trigger requires the borrower's present address be outside the U.S./territories; residences[0].propertyInformation countryCode='US', stateCode='CO' (Crystal Hills, CO) -- provably a U.S. address.</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -13176,20 +13232,24 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr"/>
+          <t>Trigger requires nontraditional credit (a borrower without a usable credit score); the sole borrower has all three bureau scores extracted: experian=742, transunion=740, equifax=724, with a traditional Credit Report documents[0] in the closed doc inventory. Nontraditional-credit provisions provably cannot attach.</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13234,20 +13294,24 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr"/>
+          <t>Trigger requires nontraditional credit (a borrower without a usable credit score); the sole borrower has all three bureau scores extracted: experian=742, transunion=740, equifax=724, with a traditional Credit Report documents[0] in the closed doc inventory. Nontraditional-credit provisions provably cannot attach.</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13292,20 +13356,24 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr"/>
+          <t>Trigger requires nontraditional credit (a borrower without a usable credit score); the sole borrower has all three bureau scores extracted: experian=742, transunion=740, equifax=724, with a traditional Credit Report documents[0] in the closed doc inventory. Nontraditional-credit provisions provably cannot attach.</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13350,20 +13418,24 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr"/>
+          <t>Trigger requires nontraditional credit (a borrower without a usable credit score); the sole borrower has all three bureau scores extracted: experian=742, transunion=740, equifax=724, with a traditional Credit Report documents[0] in the closed doc inventory. Nontraditional-credit provisions provably cannot attach.</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13470,20 +13542,24 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr"/>
+          <t>Trigger requires nontraditional credit (a borrower without a usable credit score); the sole borrower has all three bureau scores extracted: experian=742, transunion=740, equifax=724, with a traditional Credit Report documents[0] in the closed doc inventory. Nontraditional-credit provisions provably cannot attach.</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13528,20 +13604,24 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr"/>
+          <t>Trigger requires nontraditional credit (a borrower without a usable credit score); the sole borrower has all three bureau scores extracted: experian=742, transunion=740, equifax=724, with a traditional Credit Report documents[0] in the closed doc inventory. Nontraditional-credit provisions provably cannot attach.</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -19576,20 +19656,24 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L291" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (cash-out refinance on a recently acquired property); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -20516,20 +20600,24 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L307" t="inlineStr"/>
+          <t>Trigger scope is 'loans sold to Freddie Mac'; this loan is positively identified as FNMA: loanProduct.productPortfolioName='FNMA', investorGuidelineName='FNMA', under the table's QC_Policy='Fannie Mae' premise. Flagged: these are origination-side investor identification fields; the post-closing sale record itself is not extracted.</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -22754,20 +22842,24 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L344" t="inlineStr"/>
+          <t>Qualifying income is fully enumerated and closes exactly: currentIncome[0..4].basePay = 6500+6000+(-2000)+5000+4000 = 19500.0 = incomeAnalysis.qualifyingIncome = qualification.totalMonthlyIncomeAmount, matching the 5 employers (Kraft Foods W-2 + 4 self-owned businesses); otherIncomeDetail=null. No other income source participates in qualification. Trigger requires income paid in virtual currency used for qualification; every enumerated source is employment income documented in USD (W2, Paystubs, Work Number Verification, 1040s in the closed doc inventory).</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -24182,20 +24274,24 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L368" t="inlineStr"/>
+          <t>Conjunctive trigger (3rd-party VOE vendor was not Equifax/TWN AND manual NPPI process not followed); first conjunct provably false: documents[61] documentType='Work Number Verification' -- The Work Number (Equifax/TWN) is the evidenced 3rd-party VOE vendor, and the closed-world documents[] contains no other VOE vendor's documentType.</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -25184,20 +25280,24 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L385" t="inlineStr"/>
+          <t>Qualifying income is fully enumerated and closes exactly: currentIncome[0..4].basePay = 6500+6000+(-2000)+5000+4000 = 19500.0 = incomeAnalysis.qualifyingIncome = qualification.totalMonthlyIncomeAmount, matching the 5 employers (Kraft Foods W-2 + 4 self-owned businesses); otherIncomeDetail=null. No other income source participates in qualification. Trigger requires rental income used for qualifying; the REO's rental (gross 3000, net -362, RetainForRental) is not among the enumerated qualifying sources and incomeAnalysis.rental=null.</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -25358,20 +25458,24 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Only applies when rental income is relied on for qualifying; no closed-list document exactly names 'Schedule E' or the lease-in-lieu-of scenario.</t>
-        </is>
-      </c>
-      <c r="L388" t="inlineStr"/>
+          <t>Trigger requires a lease to have been used in place of IRS Form 1040 Schedule E to document rental income; the closed-world 62-entry documents[] (complete per the Touchless contract) contains no lease/rental-agreement documentType -- a lease cannot have been used if none exists in the complete file inventory. Document-usage trigger, falsified by closed-world absence, not a pass argument. (Replaces existing UNKNOWN row.)</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -27206,20 +27310,24 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L418" t="inlineStr"/>
+          <t>Qualifying income is fully enumerated and closes exactly: currentIncome[0..4].basePay = 6500+6000+(-2000)+5000+4000 = 19500.0 = incomeAnalysis.qualifyingIncome = qualification.totalMonthlyIncomeAmount, matching the 5 employers (Kraft Foods W-2 + 4 self-owned businesses); otherIncomeDetail=null. No other income source participates in qualification. Trigger requires anticipated income (employment not yet started) used in qualification; all 5 employers have employment.employmentStatusType='Current' and no employment offer/contract documentType exists in the closed doc inventory.</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -27264,20 +27372,24 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L419" t="inlineStr"/>
+          <t>Qualifying income is fully enumerated and closes exactly: currentIncome[0..4].basePay = 6500+6000+(-2000)+5000+4000 = 19500.0 = incomeAnalysis.qualifyingIncome = qualification.totalMonthlyIncomeAmount, matching the 5 employers (Kraft Foods W-2 + 4 self-owned businesses); otherIncomeDetail=null. No other income source participates in qualification. Trigger requires anticipated income used; all 5 employers are employmentStatusType='Current' (positive) and the closed-world documents[] contains no employment offer/contract documentType.</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -27322,20 +27434,24 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L420" t="inlineStr"/>
+          <t>Qualifying income is fully enumerated and closes exactly: currentIncome[0..4].basePay = 6500+6000+(-2000)+5000+4000 = 19500.0 = incomeAnalysis.qualifyingIncome = qualification.totalMonthlyIncomeAmount, matching the 5 employers (Kraft Foods W-2 + 4 self-owned businesses); otherIncomeDetail=null. No other income source participates in qualification. Trigger requires anticipated income from an employment offer/contract; all 5 employers are 'Current' and no offer/contract documentType exists in the closed doc inventory.</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -28812,20 +28928,24 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L445" t="inlineStr"/>
+          <t>Qualifying income is fully enumerated and closes exactly: currentIncome[0..4].basePay = 6500+6000+(-2000)+5000+4000 = 19500.0 = incomeAnalysis.qualifyingIncome = qualification.totalMonthlyIncomeAmount, matching the 5 employers (Kraft Foods W-2 + 4 self-owned businesses); otherIncomeDetail=null. No other income source participates in qualification. Trigger requires rental income from a live-in personal assistant of a disabled borrower; no such source is among the enumerated qualifying income.</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -29118,20 +29238,24 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L450" t="inlineStr"/>
+          <t>Qualifying income is fully enumerated and closes exactly: currentIncome[0..4].basePay = 6500+6000+(-2000)+5000+4000 = 19500.0 = incomeAnalysis.qualifyingIncome = qualification.totalMonthlyIncomeAmount, matching the 5 employers (Kraft Foods W-2 + 4 self-owned businesses); otherIncomeDetail=null. No other income source participates in qualification. Trigger requires employment-related assets used as qualifying income; every enumerated qualifying source is current employment income, not asset depletion.</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -29362,20 +29486,24 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L454" t="inlineStr"/>
+          <t>Qualifying income is fully enumerated and closes exactly: currentIncome[0..4].basePay = 6500+6000+(-2000)+5000+4000 = 19500.0 = incomeAnalysis.qualifyingIncome = qualification.totalMonthlyIncomeAmount, matching the 5 employers (Kraft Foods W-2 + 4 self-owned businesses); otherIncomeDetail=null. No other income source participates in qualification. Trigger requires virtual currency considered as an asset-based income type; no asset-based income exists among the enumerated qualifying sources.</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -29420,20 +29548,24 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L455" t="inlineStr"/>
+          <t>Trigger requires income from a non-occupant borrower; borrowersDetail.borrowerPairs has exactly 1 pair containing exactly 1 borrower (Andy America), who intends to occupy (declaration.intentToOccupyType='Yes'). No non-occupant borrower exists.</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -29788,20 +29920,24 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L461" t="inlineStr"/>
+          <t>Qualifying income is fully enumerated and closes exactly: currentIncome[0..4].basePay = 6500+6000+(-2000)+5000+4000 = 19500.0 = incomeAnalysis.qualifyingIncome = qualification.totalMonthlyIncomeAmount, matching the 5 employers (Kraft Foods W-2 + 4 self-owned businesses); otherIncomeDetail=null. No other income source participates in qualification. Trigger requires a military Leave and Earnings Statement used in lieu of a verbal VOE; the closed-world documents[] contains no LES documentType (a document-usage trigger, falsifiable by closed-world absence), militaryService=null, and all enumerated income is from 5 civilian employers (positions: Assistant Project Manager, President, Owner).</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -29908,20 +30044,24 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L463" t="inlineStr"/>
+          <t>Qualifying income is fully enumerated and closes exactly: currentIncome[0..4].basePay = 6500+6000+(-2000)+5000+4000 = 19500.0 = incomeAnalysis.qualifyingIncome = qualification.totalMonthlyIncomeAmount, matching the 5 employers (Kraft Foods W-2 + 4 self-owned businesses); otherIncomeDetail=null. No other income source participates in qualification. Trigger requires trust income (employment-related assets placed in trust) used in qualification; no trust income is among the enumerated sources and no trust-related documentType exists in the closed doc inventory.</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -32719,20 +32859,24 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>Whether the property is in an SFHA requires reading the flood determination's content, not just knowing the document type exists in inventory; escrow establishment is also not itself a document fact.</t>
-        </is>
-      </c>
-      <c r="L510" t="inlineStr"/>
+          <t>Trigger requires the subject property be located in an SFHA (flood-insurance escrow); the extracted flood determination is specialFloodHazardAreaIndicator='No', nfipFloodZoneIdentifier='X' -- provably not in an SFHA. The FEMA disaster declaration DR-4909-HI in the payload is a disaster record, not an SFHA determination. (Replaces existing UNKNOWN row.)</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -32777,20 +32921,24 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L511" t="inlineStr"/>
+          <t>Federal flood-insurance requirements (including deductibles) trigger only for a property in a Special Flood Hazard Area; the extracted flood determination is specialFloodHazardAreaIndicator='No', nfipFloodZoneIdentifier='X' -- provably not in an SFHA. Note: the FEMA disaster declaration DR-4909-HI in the payload is a disaster record, not an SFHA determination, and does not affect this trigger.</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -33195,20 +33343,24 @@
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>Only applies to this specific SFHA-plus-private-policy scenario; the private flood insurance policy isn't in the closed vocabulary.</t>
-        </is>
-      </c>
-      <c r="L518" t="inlineStr"/>
+          <t>Conjunctive trigger (property in SFHA AND a private flood insurance policy received); the SFHA conjunct is provably false: specialFloodHazardAreaIndicator='No', nfipFloodZoneIdentifier='X'. Corroborating, not load-bearing: no flood-insurance-policy documentType in the closed-world inventory. (Replaces existing UNKNOWN row.)</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -35505,20 +35657,24 @@
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K557" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L557" t="inlineStr"/>
+          <t>Federal flood-insurance requirements (including deductibles) trigger only for a property in a Special Flood Hazard Area; the extracted flood determination is specialFloodHazardAreaIndicator='No', nfipFloodZoneIdentifier='X' -- provably not in an SFHA. Note: the FEMA disaster declaration DR-4909-HI in the payload is a disaster record, not an SFHA determination, and does not affect this trigger.</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -35563,20 +35719,24 @@
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>Whether flood insurance is required is read from inside the flood determination, not from doc inventory; 'flood insurance policy' is distinct from the closed list's Flood/Standard Flood Hazard Determination form entries, so no confident document match.</t>
-        </is>
-      </c>
-      <c r="L558" t="inlineStr"/>
+          <t>Trigger is the 'if required' federal flood insurance policy-content check; flood insurance is not required: specialFloodHazardAreaIndicator='No', nfipFloodZoneIdentifier='X' (not in an SFHA). Corroborating: no flood-insurance-policy documentType in the closed-world inventory and annualFloodInsuranceAmount=null. The SFHDF-presence half of the parent question is satisfied by the present 'Standard Flood Hazard Determination' doc -- context only, not the NA ground. (Replaces existing UNKNOWN row.)</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -36209,20 +36369,24 @@
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K569" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L569" t="inlineStr"/>
+          <t>Conjunctive trigger (eMortgage AND special-purpose product requiring additional legal documents); the special-purpose conjunct is provably false by positive facts: productName='Conventional Fixed' purchase, stateCode='HI' (not a Texas 50(a)(6)), renovationLoanIndicator=null with zero renovation docs (not HomeStyle), propertyEstateType='FeeSimple' with no CLT/shared-equity docs. One false conjunct falsifies the trigger; e-closing status itself remains UNKNOWN and is not relied on.</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -37049,20 +37213,24 @@
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K583" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L583" t="inlineStr"/>
+          <t>Trigger requires a Texas Equity Section 50(a)(6) loan, which exists only as a lien on a Texas homestead; subject property stateCode='HI' (Keaau, Hawaii County). Additionally the loan is a PURCHASE, and a 50(a)(6) is an equity/cash-out lien.</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -37769,20 +37937,24 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L595" t="inlineStr"/>
+          <t>Trigger requires a Texas Equity Section 50(a)(6) loan, which exists only as a lien on a Texas homestead; subject property stateCode='HI' (Keaau, Hawaii County). Additionally the loan is a PURCHASE, and a 50(a)(6) is an equity/cash-out lien.</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -38535,20 +38707,24 @@
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K608" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L608" t="inlineStr"/>
+          <t>Trigger requires a Power of Attorney signing; the closed-world 62-entry documents[] contains no Power of Attorney documentType (a POA instrument must be in the closing file when used), and borrower-executed affidavits (Signature Name Affidavit, Occupancy Affidavit) evidence personal signing.</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -38655,20 +38831,24 @@
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K610" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L610" t="inlineStr"/>
+          <t>Trigger requires a Power of Attorney signing; the closed-world 62-entry documents[] contains no Power of Attorney documentType (a POA instrument must be in the closing file when used), and borrower-executed affidavits (Signature Name Affidavit, Occupancy Affidavit) evidence personal signing.</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -39785,20 +39965,24 @@
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K629" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L629" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (limited cash-out refinance); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_limited_cash_out_refinance == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -39843,20 +40027,24 @@
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K630" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L630" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (limited cash-out refinance); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_limited_cash_out_refinance == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -39963,20 +40151,24 @@
       </c>
       <c r="I632" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K632" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L632" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (limited cash-out refinance); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_limited_cash_out_refinance == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -40331,20 +40523,24 @@
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L638" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (cash-out refinance); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_cash_out_refinance == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -40451,20 +40647,24 @@
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L640" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (cash-out refinance); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_cash_out_refinance == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -40819,20 +41019,24 @@
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L646" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (cash-out refinance); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_cash_out_refinance == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -40877,20 +41081,24 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L647" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -41183,20 +41391,24 @@
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L652" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -41427,20 +41639,24 @@
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K656" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L656" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -41485,20 +41701,24 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L657" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -41543,20 +41763,24 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L658" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -41601,20 +41825,24 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L659" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -41659,20 +41887,24 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L660" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -41717,20 +41949,24 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L661" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -41837,20 +42073,24 @@
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L663" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -41895,20 +42135,24 @@
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L664" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -41953,20 +42197,24 @@
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L665" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -42011,20 +42259,24 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L666" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -42069,20 +42321,24 @@
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L667" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -42189,20 +42445,24 @@
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L669" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -42247,20 +42507,24 @@
       </c>
       <c r="I670" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L670" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -42305,20 +42569,24 @@
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L671" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -42363,20 +42631,24 @@
       </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K672" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L672" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -42669,20 +42941,24 @@
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L677" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -42789,20 +43065,24 @@
       </c>
       <c r="I679" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K679" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L679" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (RefiNow); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_refinow == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -43095,20 +43375,24 @@
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L684" t="inlineStr"/>
+          <t>Trigger presupposes a refinance transaction (limited cash-out refinance subject loan); loanSummary.loanTerms.loanPurposeType='PURCHASE' (positive extracted enum, single-valued) -- not any refinance type. Corroborated: Purchase Agreement in closed-world documents[13] and purchasePriceAmount=352000 (a refinance has neither). Every branch of the trigger requires a refinance, so the disjunction rule is satisfied.</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_any_refinance_type == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -43339,20 +43623,24 @@
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K688" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L688" t="inlineStr"/>
+          <t>Trigger requires the mortgage proceeds to pay off an installment land contract (contract for deed); the payoff's own contract must be in the closed file and no installment-land-contract/contract-for-deed documentType exists in the closed-world documents[]; the sale document is a standard Purchase Agreement documents[13]. Corroborating null: conversionOfContractForDeedIndicator=null.</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -43397,20 +43685,24 @@
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L689" t="inlineStr"/>
+          <t>Trigger requires the mortgage proceeds to pay off an installment land contract (contract for deed); the payoff's own contract must be in the closed file and no installment-land-contract/contract-for-deed documentType exists in the closed-world documents[]; the sale document is a standard Purchase Agreement documents[13]. Corroborating null: conversionOfContractForDeedIndicator=null.</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -43455,20 +43747,24 @@
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L690" t="inlineStr"/>
+          <t>Trigger requires the mortgage proceeds to pay off an installment land contract (contract for deed); the payoff's own contract must be in the closed file and no installment-land-contract/contract-for-deed documentType exists in the closed-world documents[]; the sale document is a standard Purchase Agreement documents[13]. Corroborating null: conversionOfContractForDeedIndicator=null.</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -43571,20 +43867,24 @@
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
         <is>
-          <t>Only applies to non-SOFR ARM loans, a loan-product fact not derivable from the document inventory; the Note and Riders are explicitly named.</t>
-        </is>
-      </c>
-      <c r="L692" t="inlineStr"/>
+          <t>Trigger requires a non-SOFR ARM loan; loanSummary.amortization.amortizationType='FIXED' and productName='Conventional Fixed' -- provably not an ARM. (Replaces existing UNKNOWN row, whose reason 'amortization type explicitly UNKNOWN' is contradicted by this extracted field.)</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_arm == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -43749,20 +44049,24 @@
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L695" t="inlineStr"/>
+          <t>Trigger requires an ARM; loanSummary.amortization.amortizationType='FIXED' and productName='Conventional Fixed' -- positive extracted facts, provably not an ARM.</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.ContextFlag_loan_product_arm == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -44915,20 +45219,24 @@
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L714" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -44973,20 +45281,24 @@
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L715" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -45093,20 +45405,24 @@
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L717" t="inlineStr"/>
+          <t>Trigger requires a HomeStyle Renovation loan; provably not one: productName='Conventional Fixed' (positive product identification), zero renovation (contract, plans, escrow, completion) documentTypes in the closed-world 62-entry documents[], on a standard purchase of an existing home (Purchase Agreement + full URAR). Corroborating null: renovationLoanIndicator=null.</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -45213,20 +45529,24 @@
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L719" t="inlineStr"/>
+          <t>Trigger requires a HomeStyle Renovation loan; provably not one: productName='Conventional Fixed' (positive product identification), zero renovation (contract, plans, escrow, completion) documentTypes in the closed-world 62-entry documents[], on a standard purchase of an existing home (Purchase Agreement + full URAR). Corroborating null: renovationLoanIndicator=null.</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -45271,20 +45591,24 @@
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L720" t="inlineStr"/>
+          <t>Trigger requires a HomeStyle Renovation loan; provably not one: productName='Conventional Fixed' (positive product identification), zero renovation (contract, plans, escrow, completion) documentTypes in the closed-world 62-entry documents[], on a standard purchase of an existing home (Purchase Agreement + full URAR). Corroborating null: renovationLoanIndicator=null.</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -45453,20 +45777,24 @@
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L723" t="inlineStr"/>
+          <t>Trigger requires a HomeStyle Renovation loan; provably not one: productName='Conventional Fixed' (positive product identification), zero renovation (contract, plans, escrow, completion) documentTypes in the closed-world 62-entry documents[], on a standard purchase of an existing home (Purchase Agreement + full URAR). Corroborating null: renovationLoanIndicator=null.</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -45573,20 +45901,24 @@
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L725" t="inlineStr"/>
+          <t>Trigger requires a HomeStyle Energy loan; provably not one: productName='Conventional Fixed' (positive product identification), zero energy-report/energy-improvement documentTypes in the closed-world 62-entry documents[], on a standard purchase of an existing home (Purchase Agreement + full URAR). Corroborating null: renovationLoanIndicator=null.</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -45693,20 +46025,24 @@
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L727" t="inlineStr"/>
+          <t>Trigger requires a HomeStyle Energy loan; provably not one: productName='Conventional Fixed' (positive product identification), zero energy-report/energy-improvement documentTypes in the closed-world 62-entry documents[], on a standard purchase of an existing home (Purchase Agreement + full URAR). Corroborating null: renovationLoanIndicator=null.</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -45751,20 +46087,24 @@
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L728" t="inlineStr"/>
+          <t>Trigger requires a HomeStyle Energy loan; provably not one: productName='Conventional Fixed' (positive product identification), zero energy-report/energy-improvement documentTypes in the closed-world 62-entry documents[], on a standard purchase of an existing home (Purchase Agreement + full URAR). Corroborating null: renovationLoanIndicator=null.</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -45929,20 +46269,24 @@
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L731" t="inlineStr"/>
+          <t>Trigger requires a HomeStyle Energy loan; provably not one: productName='Conventional Fixed' (positive product identification), zero energy-report/energy-improvement documentTypes in the closed-world 62-entry documents[], on a standard purchase of an existing home (Purchase Agreement + full URAR). Corroborating null: renovationLoanIndicator=null.</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -45987,20 +46331,24 @@
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L732" t="inlineStr"/>
+          <t>Trigger requires a Texas Equity Section 50(a)(6) loan, which exists only as a lien on a Texas homestead; subject property stateCode='HI' (Keaau, Hawaii County). Additionally the loan is a PURCHASE, and a 50(a)(6) is an equity/cash-out lien.</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -46107,20 +46455,24 @@
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L734" t="inlineStr"/>
+          <t>Trigger requires a Texas Equity Section 50(a)(6) loan, which exists only as a lien on a Texas homestead; subject property stateCode='HI' (Keaau, Hawaii County). Additionally the loan is a PURCHASE, and a 50(a)(6) is an equity/cash-out lien.</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -46227,20 +46579,24 @@
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L736" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing or a Community Land Trust / shared-equity / resale-restricted property; additionally propertyEstateType='FeeSimple' (a CLT is a leasehold on trust land) and the only project rider in the closed doc inventory is a PUD Rider documents[16] -- no CLT ground lease or resale-restriction rider exists; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -46343,20 +46699,24 @@
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L738" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -46463,20 +46823,24 @@
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L740" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -46521,20 +46885,24 @@
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L741" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -46579,20 +46947,24 @@
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L742" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -46637,20 +47009,24 @@
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K743" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L743" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -46695,20 +47071,24 @@
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K744" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L744" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -46815,20 +47195,24 @@
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L746" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing or a Community Land Trust / shared-equity / resale-restricted property; additionally propertyEstateType='FeeSimple' (a CLT is a leasehold on trust land) and the only project rider in the closed doc inventory is a PUD Rider documents[16] -- no CLT ground lease or resale-restriction rider exists; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -46935,20 +47319,24 @@
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L748" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing or a Community Land Trust / shared-equity / resale-restricted property; additionally propertyEstateType='FeeSimple' (a CLT is a leasehold on trust land) and the only project rider in the closed doc inventory is a PUD Rider documents[16] -- no CLT ground lease or resale-restriction rider exists; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -47113,20 +47501,24 @@
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K751" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L751" t="inlineStr"/>
+          <t>Trigger requires a HomeReady transaction; loanProduct.productName='Conventional Fixed' and productPortfolioName='FNMA' -- positive product identification of a standard conventional product, not HomeReady. Auxiliary context: qualifying income totalMonthlyIncomeAmount=19500/mo, inconsistent with an income-limited affordable product. Polarity checked: the defect condition attaches only inside a HomeReady transaction, 'not HomeReady' is the exemption here, not the trigger.</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -47171,20 +47563,24 @@
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K752" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L752" t="inlineStr"/>
+          <t>Trigger requires a HomeReady transaction; loanProduct.productName='Conventional Fixed' and productPortfolioName='FNMA' -- positive product identification of a standard conventional product, not HomeReady. Auxiliary context: qualifying income totalMonthlyIncomeAmount=19500/mo, inconsistent with an income-limited affordable product. Polarity checked: the defect condition attaches only inside a HomeReady transaction, 'not HomeReady' is the exemption here, not the trigger. Additionally the 95.01-97% LTV band conjunct is independently false: ltv=73.8637.</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -47291,20 +47687,24 @@
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K754" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L754" t="inlineStr"/>
+          <t>Trigger requires a HomeReady transaction; loanProduct.productName='Conventional Fixed' and productPortfolioName='FNMA' -- positive product identification of a standard conventional product, not HomeReady. Auxiliary context: qualifying income totalMonthlyIncomeAmount=19500/mo, inconsistent with an income-limited affordable product. Polarity checked: the defect condition attaches only inside a HomeReady transaction, 'not HomeReady' is the exemption here, not the trigger.</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -47349,20 +47749,24 @@
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K755" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L755" t="inlineStr"/>
+          <t>Trigger requires a HomeReady transaction; loanProduct.productName='Conventional Fixed' and productPortfolioName='FNMA' -- positive product identification of a standard conventional product, not HomeReady. Auxiliary context: qualifying income totalMonthlyIncomeAmount=19500/mo, inconsistent with an income-limited affordable product. Polarity checked: the defect condition attaches only inside a HomeReady transaction, 'not HomeReady' is the exemption here, not the trigger.</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -47655,20 +48059,24 @@
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K760" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L760" t="inlineStr"/>
+          <t>Trigger requires a HomeReady transaction; loanProduct.productName='Conventional Fixed' and productPortfolioName='FNMA' -- positive product identification of a standard conventional product, not HomeReady. Auxiliary context: qualifying income totalMonthlyIncomeAmount=19500/mo, inconsistent with an income-limited affordable product. Polarity checked: the defect condition attaches only inside a HomeReady transaction, 'not HomeReady' is the exemption here, not the trigger.</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -47775,20 +48183,24 @@
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K762" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L762" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -47833,20 +48245,24 @@
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K763" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L763" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -48139,20 +48555,24 @@
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K768" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L768" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -48197,20 +48617,24 @@
       </c>
       <c r="I769" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J769" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K769" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L769" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -48255,20 +48679,24 @@
       </c>
       <c r="I770" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K770" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L770" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -48313,20 +48741,24 @@
       </c>
       <c r="I771" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J771" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K771" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L771" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -48557,20 +48989,24 @@
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J775" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K775" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L775" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -48615,20 +49051,24 @@
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J776" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K776" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L776" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -48735,20 +49175,24 @@
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K778" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L778" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -48917,20 +49361,24 @@
       </c>
       <c r="I781" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J781" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K781" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L781" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -48975,20 +49423,24 @@
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K782" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L782" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -49033,20 +49485,24 @@
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K783" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L783" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -49091,20 +49547,24 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K784" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L784" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -49149,20 +49609,24 @@
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K785" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L785" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -49207,20 +49671,24 @@
       </c>
       <c r="I786" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K786" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L786" t="inlineStr"/>
+          <t>Trigger requires a construction-to-permanent (CTP) transaction; provably not CTP by positive facts, not null-inference alone: loanPurposeType='PURCHASE' (positive enum); the closed-world 62-entry documents[] (complete per the Touchless contract) contains zero construction documentTypes -- no construction loan agreement, construction rider, draw schedule, or conversion/modification agreement, all of which a CTP closing package must contain; standard resale Purchase Agreement documents[13] and permanent Note documents[35] are present. Corroborating nulls: loanSummary.construction=null, constructionLoanIndicator=null, constructionToPermanentClosingType=null.</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -50059,20 +50527,24 @@
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K800" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L800" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing or a Community Land Trust / shared-equity / resale-restricted property; additionally propertyEstateType='FeeSimple' (a CLT is a leasehold on trust land) and the only project rider in the closed doc inventory is a PUD Rider documents[16] -- no CLT ground lease or resale-restriction rider exists; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -50365,20 +50837,24 @@
       </c>
       <c r="I805" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K805" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L805" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing or a Community Land Trust / shared-equity / resale-restricted property; additionally propertyEstateType='FeeSimple' (a CLT is a leasehold on trust land) and the only project rider in the closed doc inventory is a PUD Rider documents[16] -- no CLT ground lease or resale-restriction rider exists; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -50485,20 +50961,24 @@
       </c>
       <c r="I807" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K807" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L807" t="inlineStr"/>
+          <t>Trigger requires subordinate/community-second financing or a Community Land Trust / shared-equity / resale-restricted property; additionally propertyEstateType='FeeSimple' (a CLT is a leasehold on trust land) and the only project rider in the closed doc inventory is a PUD Rider documents[16] -- no CLT ground lease or resale-restriction rider exists; no subordinate financing exists: ltv=cltv=hcltv=73.86 (CLTV and HCLTV exactly equal to LTV proves no subordinate lien, drawn or undrawn, in the ratios), lienPriorityType='FirstLien', subordinateLienAmount=null, and the closed-world documents[] contains exactly one Note (documents[35]) and one Security Instrument (documents[53]) -- no second note/deed of trust.</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -50771,20 +51251,24 @@
       <c r="H812" t="inlineStr"/>
       <c r="I812" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K812" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L812" t="inlineStr"/>
+          <t>Card applicability requires Loans.LoanType='Portfolio' (lender portfolio / private-bank variance program); the loan is positively identified as an agency FNMA loan: loanProduct.productPortfolioName='FNMA', investorGuidelineName='FNMA', consistent with the table's own QC_Policy='Fannie Mae' premise. Flagged: LoanType is identified via product/investor fields, not a literal LoanType field.</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.LoanType == 'Portfolio' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -51235,20 +51719,24 @@
       </c>
       <c r="I820" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J820" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K820" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L820" t="inlineStr"/>
+          <t>Trigger requires the subject be held as a leasehold estate; propertyDetail.propertyEstateType='FeeSimple' (positive extracted enum) directly contradicts a leasehold.</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -51293,20 +51781,24 @@
       </c>
       <c r="I821" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K821" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L821" t="inlineStr"/>
+          <t>Trigger requires the subject be held as a leasehold estate; propertyDetail.propertyEstateType='FeeSimple' (positive extracted enum) directly contradicts a leasehold.</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -51413,20 +51905,24 @@
       </c>
       <c r="I823" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K823" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L823" t="inlineStr"/>
+          <t>Trigger requires the subject be held as a leasehold estate; propertyDetail.propertyEstateType='FeeSimple' (positive extracted enum) directly contradicts a leasehold.</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -51657,20 +52153,24 @@
       </c>
       <c r="I827" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K827" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L827" t="inlineStr"/>
+          <t>Trigger requires the subject be held as a leasehold estate; propertyDetail.propertyEstateType='FeeSimple' (positive extracted enum) directly contradicts a leasehold.</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -52307,24 +52807,20 @@
       </c>
       <c r="I838" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>NOT_COMPILED</t>
         </is>
       </c>
       <c r="J838" t="inlineStr">
         <is>
-          <t>PRECONDITION_NOT_APPLICABLE</t>
+          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
         </is>
       </c>
       <c r="K838" t="inlineStr">
         <is>
-          <t>No disaster impact to the property is evidenced anywhere in the profile.</t>
-        </is>
-      </c>
-      <c r="L838" t="inlineStr">
-        <is>
-          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
-        </is>
-      </c>
+          <t>Only applies when the subject property was affected by a disaster, a property-condition fact not derivable from document inventory.</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -53201,20 +53697,24 @@
       </c>
       <c r="I853" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K853" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L853" t="inlineStr"/>
+          <t>Trigger requires a desktop appraisal to have been used; the appraisal of record in the closed doc inventory is documents[52] 'Form 1004 Uniform Residential Appraisal' (a full traditional URAR), and no desktop-appraisal form documentType exists anywhere in the closed-world 62-entry inventory.</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -53321,20 +53821,24 @@
       </c>
       <c r="I855" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J855" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K855" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L855" t="inlineStr"/>
+          <t>Trigger requires a hybrid appraisal to have been used; the appraisal of record in the closed doc inventory is documents[52] 'Form 1004 Uniform Residential Appraisal' (a full traditional URAR), and no hybrid-appraisal form documentType exists anywhere in the closed-world 62-entry inventory.</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -56227,20 +56731,24 @@
       </c>
       <c r="I904" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J904" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K904" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L904" t="inlineStr"/>
+          <t>Trigger requires value acceptance (appraisal waiver) to have been the transaction's valuation path; the valuation of record is a full traditional appraisal: documents[52] 'Form 1004 Uniform Residential Appraisal' plus a populated valuationServices[0].valuationReport used for the collateral valuation (352000); piw=null, ace=null. Matches the table's established standard (existing NA rows O-FNM-55740/56088/56225/56231/56232/56227, incl. same-card siblings).</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
@@ -56347,20 +56855,24 @@
       </c>
       <c r="I906" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J906" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K906" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L906" t="inlineStr"/>
+          <t>Trigger requires value acceptance (appraisal waiver) to have been the transaction's valuation path; the valuation of record is a full traditional appraisal: documents[52] 'Form 1004 Uniform Residential Appraisal' plus a populated valuationServices[0].valuationReport used for the collateral valuation (352000); piw=null, ace=null. Matches the table's established standard (existing NA rows O-FNM-55740/56088/56225/56231/56232/56227, incl. same-card siblings).</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
@@ -56467,20 +56979,24 @@
       </c>
       <c r="I908" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J908" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K908" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L908" t="inlineStr"/>
+          <t>Trigger requires value acceptance (appraisal waiver) to have been the transaction's valuation path; the valuation of record is a full traditional appraisal: documents[52] 'Form 1004 Uniform Residential Appraisal' plus a populated valuationServices[0].valuationReport used for the collateral valuation (352000); piw=null, ace=null. Matches the table's established standard (existing NA rows O-FNM-55740/56088/56225/56231/56232/56227, incl. same-card siblings).</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
@@ -56649,20 +57165,24 @@
       </c>
       <c r="I911" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J911" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K911" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L911" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType == 'Condominium' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -56769,20 +57289,24 @@
       </c>
       <c r="I913" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J913" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K913" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L913" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType == 'Condominium' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -56889,20 +57413,24 @@
       </c>
       <c r="I915" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J915" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K915" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L915" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType == 'Condominium' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
@@ -56947,20 +57475,24 @@
       </c>
       <c r="I916" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J916" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K916" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L916" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType == 'Condominium' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -57067,20 +57599,24 @@
       </c>
       <c r="I918" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J918" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K918" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L918" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
@@ -57125,20 +57661,24 @@
       </c>
       <c r="I919" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J919" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K919" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L919" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -57245,20 +57785,24 @@
       </c>
       <c r="I921" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J921" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K921" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L921" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -57303,20 +57847,24 @@
       </c>
       <c r="I922" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J922" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K922" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L922" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -57361,20 +57909,24 @@
       </c>
       <c r="I923" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J923" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K923" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L923" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
@@ -57481,20 +58033,24 @@
       </c>
       <c r="I925" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J925" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K925" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L925" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
@@ -57663,20 +58219,24 @@
       </c>
       <c r="I928" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J928" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K928" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L928" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
@@ -57969,20 +58529,24 @@
       </c>
       <c r="I933" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J933" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K933" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L933" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -58027,20 +58591,24 @@
       </c>
       <c r="I934" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J934" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K934" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L934" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -58147,20 +58715,24 @@
       </c>
       <c r="I936" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J936" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K936" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L936" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -58697,20 +59269,24 @@
       </c>
       <c r="I945" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J945" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K945" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L945" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
@@ -58755,20 +59331,24 @@
       </c>
       <c r="I946" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J946" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K946" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L946" t="inlineStr"/>
+          <t>Trigger requires a condominium or cooperative project; both any_of branches provably false: attachmentType='Detached', projectLegalStructureType='Detached', pudIndicator='Y' (detached single-family home in a PUD), condominiumIndicator=null, cooperativeIndicator=null, and the closed doc inventory carries a 'PUD Rider' documents[16], not a condo/co-op rider.</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>Precondition not met: Loans.PropertyType in 'Condominium|Cooperative' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
@@ -59637,20 +60217,24 @@
       </c>
       <c r="I961" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J961" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K961" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L961" t="inlineStr"/>
+          <t>Trigger requires value acceptance + property data (appraisal waiver) to have been the transaction's valuation path; the valuation of record is a full traditional appraisal: documents[52] 'Form 1004 Uniform Residential Appraisal' plus a populated valuationServices[0].valuationReport used for the collateral valuation (352000); piw=null, ace=null. Matches the table's established standard (existing NA rows O-FNM-55740/56088/56225/56231/56232/56227, incl. same-card siblings).</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
@@ -59757,20 +60341,24 @@
       </c>
       <c r="I963" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J963" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K963" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L963" t="inlineStr"/>
+          <t>Trigger requires value acceptance + property data (appraisal waiver) to have been the transaction's valuation path; the valuation of record is a full traditional appraisal: documents[52] 'Form 1004 Uniform Residential Appraisal' plus a populated valuationServices[0].valuationReport used for the collateral valuation (352000); piw=null, ace=null. Matches the table's established standard (existing NA rows O-FNM-55740/56088/56225/56231/56232/56227, incl. same-card siblings).</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
@@ -59815,20 +60403,24 @@
       </c>
       <c r="I964" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J964" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K964" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L964" t="inlineStr"/>
+          <t>Trigger requires value acceptance + property data (appraisal waiver) to have been the transaction's valuation path; the valuation of record is a full traditional appraisal: documents[52] 'Form 1004 Uniform Residential Appraisal' plus a populated valuationServices[0].valuationReport used for the collateral valuation (352000); piw=null, ace=null. Matches the table's established standard (existing NA rows O-FNM-55740/56088/56225/56231/56232/56227, incl. same-card siblings).</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
@@ -59997,20 +60589,24 @@
       </c>
       <c r="I967" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J967" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K967" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L967" t="inlineStr"/>
+          <t>Trigger requires value acceptance + property data (appraisal waiver) to have been the transaction's valuation path; the valuation of record is a full traditional appraisal: documents[52] 'Form 1004 Uniform Residential Appraisal' plus a populated valuationServices[0].valuationReport used for the collateral valuation (352000); piw=null, ace=null. Matches the table's established standard (existing NA rows O-FNM-55740/56088/56225/56231/56232/56227, incl. same-card siblings).</t>
+        </is>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
@@ -60055,20 +60651,24 @@
       </c>
       <c r="I968" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J968" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K968" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L968" t="inlineStr"/>
+          <t>Trigger requires value acceptance + property data (appraisal waiver) to have been the transaction's valuation path; the valuation of record is a full traditional appraisal: documents[52] 'Form 1004 Uniform Residential Appraisal' plus a populated valuationServices[0].valuationReport used for the collateral valuation (352000); piw=null, ace=null. Matches the table's established standard (existing NA rows O-FNM-55740/56088/56225/56231/56232/56227, incl. same-card siblings).</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
@@ -60957,20 +61557,24 @@
       </c>
       <c r="I983" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J983" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K983" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L983" t="inlineStr"/>
+          <t>Trigger requires the subject be held as a leasehold estate; propertyDetail.propertyEstateType='FeeSimple' (positive extracted enum) directly contradicts a leasehold.</t>
+        </is>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
@@ -61015,20 +61619,24 @@
       </c>
       <c r="I984" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J984" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K984" t="inlineStr">
         <is>
-          <t>Property tenure is not derivable from doc inventory; the defect concerns lien-priority/legal structure, not a specific document.</t>
-        </is>
-      </c>
-      <c r="L984" t="inlineStr"/>
+          <t>Trigger requires a leasehold interest in the land; propertyDetail.propertyEstateType='FeeSimple' (positive extracted enum) -- provably not a leasehold. (Replaces existing UNKNOWN row, whose reason 'leasehold vs fee simple not stated' is contradicted by this extracted field.)</t>
+        </is>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
@@ -63709,20 +64317,24 @@
       </c>
       <c r="I1029" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J1029" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_NOT_CONVERTED_BY_DESIGN</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K1029" t="inlineStr">
         <is>
-          <t>Check type not in this build's scope (e.g. reverification / list_screening -- deliberately out of scope)</t>
-        </is>
-      </c>
-      <c r="L1029" t="inlineStr"/>
+          <t>Trigger clause requires that the applicant 'does not expressly accept or use the credit offered' after a counteroffer; the loan consummated -- executed Note documents[35], Closing Disclosure documents[34], Title Policy documents[31] -- so the credit on this application was used, falsifying that clause regardless of whether a counteroffer occurred. Flagged: one inferential step (consummation =&gt; credit used).</t>
+        </is>
+      </c>
+      <c r="L1029" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
@@ -64661,20 +65273,24 @@
       </c>
       <c r="I1045" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J1045" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K1045" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L1045" t="inlineStr"/>
+          <t>Trigger requires the subject be a second home or investment property (not owner-occupied); provably false: propertyDetail.propertyUsageType='PrimaryResidence', declaration.intentToOccupyType='Yes', and a signed Occupancy Affidavit documents[17] is in the closed doc inventory.</t>
+        </is>
+      </c>
+      <c r="L1045" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
@@ -64719,20 +65335,24 @@
       </c>
       <c r="I1046" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J1046" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K1046" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L1046" t="inlineStr"/>
+          <t>Trigger requires the subject be a second home or investment property (not owner-occupied); provably false: propertyDetail.propertyUsageType='PrimaryResidence', declaration.intentToOccupyType='Yes', and a signed Occupancy Affidavit documents[17] is in the closed doc inventory.</t>
+        </is>
+      </c>
+      <c r="L1046" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
@@ -64835,20 +65455,24 @@
       </c>
       <c r="I1048" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J1048" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K1048" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L1048" t="inlineStr"/>
+          <t>Trigger requires the subject be a second home or investment property (not owner-occupied); provably false: propertyDetail.propertyUsageType='PrimaryResidence', declaration.intentToOccupyType='Yes', and a signed Occupancy Affidavit documents[17] is in the closed doc inventory.</t>
+        </is>
+      </c>
+      <c r="L1048" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
@@ -66090,20 +66714,24 @@
       </c>
       <c r="I1069" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J1069" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_TRIGGER_GATED_NEEDS_FACT_MACHINERY</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K1069" t="inlineStr">
         <is>
-          <t>Only meaningfully applies when a borrower is a non-US citizen, a borrower attribute not determinable from document-type inventory; required residency documentation (e.g., green card/visa) is not in the closed vocabulary.</t>
-        </is>
-      </c>
-      <c r="L1069" t="inlineStr"/>
+          <t>Trigger requires a non-US-citizen borrower needing residency documentation; declaration.citizenshipResidencyType='USCitizen' for the sole borrower -- provably false. (Replaces existing UNKNOWN row; citizenship IS extracted.)</t>
+        </is>
+      </c>
+      <c r="L1069" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
@@ -66148,20 +66776,24 @@
       </c>
       <c r="I1070" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J1070" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K1070" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L1070" t="inlineStr"/>
+          <t>Trigger requires a HomeReady transaction; loanProduct.productName='Conventional Fixed' and productPortfolioName='FNMA' -- positive product identification of a standard conventional product, not HomeReady. Auxiliary context: qualifying income totalMonthlyIncomeAmount=19500/mo, inconsistent with an income-limited affordable product. Polarity checked: the defect condition attaches only inside a HomeReady transaction, 'not HomeReady' is the exemption here, not the trigger.</t>
+        </is>
+      </c>
+      <c r="L1070" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
@@ -66206,20 +66838,24 @@
       </c>
       <c r="I1071" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J1071" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K1071" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L1071" t="inlineStr"/>
+          <t>Trigger requires the subject be a second home or investment property (not owner-occupied); provably false: propertyDetail.propertyUsageType='PrimaryResidence', declaration.intentToOccupyType='Yes', and a signed Occupancy Affidavit documents[17] is in the closed doc inventory.</t>
+        </is>
+      </c>
+      <c r="L1071" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
@@ -66264,20 +66900,24 @@
       </c>
       <c r="I1072" t="inlineStr">
         <is>
-          <t>NOT_COMPILED</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="J1072" t="inlineStr">
         <is>
-          <t>NOT_COMPILED_THRESHOLD_NOT_PARSEABLE</t>
+          <t>PRECONDITION_NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K1072" t="inlineStr">
         <is>
-          <t>Rule cites a threshold but the compiler could not extract one unambiguous number+direction from the text (compile-time gap, same for every loan)</t>
-        </is>
-      </c>
-      <c r="L1072" t="inlineStr"/>
+          <t>Trigger requires the subject be a second home or investment property (not owner-occupied); provably false: propertyDetail.propertyUsageType='PrimaryResidence', declaration.intentToOccupyType='Yes', and a signed Occupancy Affidavit documents[17] is in the closed doc inventory.</t>
+        </is>
+      </c>
+      <c r="L1072" t="inlineStr">
+        <is>
+          <t>Precondition not met: _demo_scenario_gate_always_false == 'True' does not hold for this loan.</t>
+        </is>
+      </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
